--- a/icc_dataset.xlsx
+++ b/icc_dataset.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Downloads\Hrutik_pro1\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6864E005-50E1-4E26-82CA-C15B3953CCF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="60" windowWidth="9495" windowHeight="4635"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="110">
   <si>
     <t>Tournament</t>
   </si>
@@ -332,13 +338,25 @@
   </si>
   <si>
     <t>Rachin Ravindra</t>
+  </si>
+  <si>
+    <t>Sanju samson</t>
+  </si>
+  <si>
+    <t>Jasprit Bumrah</t>
+  </si>
+  <si>
+    <t>IND,NZ,SA,ENG</t>
+  </si>
+  <si>
+    <t>India/sri lanka</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -375,13 +393,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -419,7 +445,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -453,6 +479,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -487,9 +514,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -662,20 +690,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H32"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H33"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="11.42578125" customWidth="1"/>
-    <col min="3" max="4" width="16.5703125" customWidth="1"/>
-    <col min="5" max="5" width="19.85546875" customWidth="1"/>
-    <col min="6" max="6" width="19.140625" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="22.85546875" customWidth="1"/>
+    <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.7109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -701,7 +730,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -727,7 +756,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -753,7 +782,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -779,7 +808,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -805,7 +834,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -831,7 +860,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -857,7 +886,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -883,7 +912,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -909,7 +938,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -935,7 +964,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -961,7 +990,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>8</v>
       </c>
@@ -987,7 +1016,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>8</v>
       </c>
@@ -1013,7 +1042,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>8</v>
       </c>
@@ -1039,7 +1068,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>57</v>
       </c>
@@ -1065,7 +1094,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>57</v>
       </c>
@@ -1091,7 +1120,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>57</v>
       </c>
@@ -1117,7 +1146,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>57</v>
       </c>
@@ -1143,7 +1172,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>57</v>
       </c>
@@ -1169,7 +1198,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>57</v>
       </c>
@@ -1195,7 +1224,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>57</v>
       </c>
@@ -1221,7 +1250,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>57</v>
       </c>
@@ -1247,7 +1276,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>57</v>
       </c>
@@ -1273,7 +1302,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>82</v>
       </c>
@@ -1299,7 +1328,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>82</v>
       </c>
@@ -1325,7 +1354,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>82</v>
       </c>
@@ -1351,7 +1380,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>82</v>
       </c>
@@ -1377,7 +1406,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>82</v>
       </c>
@@ -1403,7 +1432,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>82</v>
       </c>
@@ -1429,7 +1458,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>82</v>
       </c>
@@ -1455,7 +1484,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>82</v>
       </c>
@@ -1481,7 +1510,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>82</v>
       </c>
@@ -1505,6 +1534,32 @@
       </c>
       <c r="H32" t="s">
         <v>105</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>82</v>
+      </c>
+      <c r="B33">
+        <v>2026</v>
+      </c>
+      <c r="C33" t="s">
+        <v>109</v>
+      </c>
+      <c r="D33" t="s">
+        <v>17</v>
+      </c>
+      <c r="E33" t="s">
+        <v>46</v>
+      </c>
+      <c r="F33" t="s">
+        <v>108</v>
+      </c>
+      <c r="G33" t="s">
+        <v>107</v>
+      </c>
+      <c r="H33" t="s">
+        <v>106</v>
       </c>
     </row>
   </sheetData>

--- a/icc_dataset.xlsx
+++ b/icc_dataset.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Downloads\Hrutik_pro1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6864E005-50E1-4E26-82CA-C15B3953CCF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52385C6A-C7F3-46C2-8996-F0C3EDE4BB0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="2460" windowWidth="20490" windowHeight="8460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="110">
   <si>
     <t>Tournament</t>
   </si>
@@ -1565,4 +1566,882 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C70B37F-E10F-4D81-9B58-548484F1E08E}">
+  <dimension ref="A1:H33"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2">
+        <v>1975</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3">
+        <v>1979</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>1983</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>1987</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>1992</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>1996</v>
+      </c>
+      <c r="C7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>1999</v>
+      </c>
+      <c r="C8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8" t="s">
+        <v>34</v>
+      </c>
+      <c r="H8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>2003</v>
+      </c>
+      <c r="C9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" t="s">
+        <v>37</v>
+      </c>
+      <c r="G9" t="s">
+        <v>38</v>
+      </c>
+      <c r="H9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>2007</v>
+      </c>
+      <c r="C10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F10" t="s">
+        <v>40</v>
+      </c>
+      <c r="G10" t="s">
+        <v>41</v>
+      </c>
+      <c r="H10" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11">
+        <v>2011</v>
+      </c>
+      <c r="C11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" t="s">
+        <v>43</v>
+      </c>
+      <c r="G11" t="s">
+        <v>44</v>
+      </c>
+      <c r="H11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12">
+        <v>2015</v>
+      </c>
+      <c r="C12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>46</v>
+      </c>
+      <c r="F12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G12" t="s">
+        <v>48</v>
+      </c>
+      <c r="H12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13">
+        <v>2019</v>
+      </c>
+      <c r="C13" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" t="s">
+        <v>46</v>
+      </c>
+      <c r="F13" t="s">
+        <v>51</v>
+      </c>
+      <c r="G13" t="s">
+        <v>52</v>
+      </c>
+      <c r="H13" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14">
+        <v>2023</v>
+      </c>
+      <c r="C14" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F14" t="s">
+        <v>54</v>
+      </c>
+      <c r="G14" t="s">
+        <v>55</v>
+      </c>
+      <c r="H14" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>57</v>
+      </c>
+      <c r="B15">
+        <v>2007</v>
+      </c>
+      <c r="C15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" t="s">
+        <v>17</v>
+      </c>
+      <c r="E15" t="s">
+        <v>24</v>
+      </c>
+      <c r="F15" t="s">
+        <v>58</v>
+      </c>
+      <c r="G15" t="s">
+        <v>59</v>
+      </c>
+      <c r="H15" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>57</v>
+      </c>
+      <c r="B16">
+        <v>2009</v>
+      </c>
+      <c r="C16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" t="s">
+        <v>29</v>
+      </c>
+      <c r="F16" t="s">
+        <v>61</v>
+      </c>
+      <c r="G16" t="s">
+        <v>60</v>
+      </c>
+      <c r="H16" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>57</v>
+      </c>
+      <c r="B17">
+        <v>2010</v>
+      </c>
+      <c r="C17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" t="s">
+        <v>63</v>
+      </c>
+      <c r="G17" t="s">
+        <v>64</v>
+      </c>
+      <c r="H17" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>57</v>
+      </c>
+      <c r="B18">
+        <v>2012</v>
+      </c>
+      <c r="C18" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18" t="s">
+        <v>29</v>
+      </c>
+      <c r="F18" t="s">
+        <v>66</v>
+      </c>
+      <c r="G18" t="s">
+        <v>67</v>
+      </c>
+      <c r="H18" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>57</v>
+      </c>
+      <c r="B19">
+        <v>2014</v>
+      </c>
+      <c r="C19" t="s">
+        <v>69</v>
+      </c>
+      <c r="D19" t="s">
+        <v>29</v>
+      </c>
+      <c r="E19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G19" t="s">
+        <v>71</v>
+      </c>
+      <c r="H19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>57</v>
+      </c>
+      <c r="B20">
+        <v>2016</v>
+      </c>
+      <c r="C20" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" t="s">
+        <v>72</v>
+      </c>
+      <c r="G20" t="s">
+        <v>67</v>
+      </c>
+      <c r="H20" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>57</v>
+      </c>
+      <c r="B21">
+        <v>2021</v>
+      </c>
+      <c r="C21" t="s">
+        <v>73</v>
+      </c>
+      <c r="D21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" t="s">
+        <v>46</v>
+      </c>
+      <c r="F21" t="s">
+        <v>74</v>
+      </c>
+      <c r="G21" t="s">
+        <v>75</v>
+      </c>
+      <c r="H21" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>57</v>
+      </c>
+      <c r="B22">
+        <v>2022</v>
+      </c>
+      <c r="C22" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F22" t="s">
+        <v>77</v>
+      </c>
+      <c r="G22" t="s">
+        <v>78</v>
+      </c>
+      <c r="H22" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>57</v>
+      </c>
+      <c r="B23">
+        <v>2024</v>
+      </c>
+      <c r="C23" t="s">
+        <v>79</v>
+      </c>
+      <c r="D23" t="s">
+        <v>17</v>
+      </c>
+      <c r="E23" t="s">
+        <v>36</v>
+      </c>
+      <c r="F23" t="s">
+        <v>80</v>
+      </c>
+      <c r="G23" t="s">
+        <v>56</v>
+      </c>
+      <c r="H23" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>82</v>
+      </c>
+      <c r="B24">
+        <v>1998</v>
+      </c>
+      <c r="C24" t="s">
+        <v>69</v>
+      </c>
+      <c r="D24" t="s">
+        <v>36</v>
+      </c>
+      <c r="E24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F24" t="s">
+        <v>83</v>
+      </c>
+      <c r="G24" t="s">
+        <v>84</v>
+      </c>
+      <c r="H24" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>82</v>
+      </c>
+      <c r="B25">
+        <v>2000</v>
+      </c>
+      <c r="C25" t="s">
+        <v>85</v>
+      </c>
+      <c r="D25" t="s">
+        <v>46</v>
+      </c>
+      <c r="E25" t="s">
+        <v>17</v>
+      </c>
+      <c r="F25" t="s">
+        <v>86</v>
+      </c>
+      <c r="G25" t="s">
+        <v>87</v>
+      </c>
+      <c r="H25" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>82</v>
+      </c>
+      <c r="B26">
+        <v>2002</v>
+      </c>
+      <c r="C26" t="s">
+        <v>29</v>
+      </c>
+      <c r="D26" t="s">
+        <v>88</v>
+      </c>
+      <c r="E26" t="s">
+        <v>14</v>
+      </c>
+      <c r="F26" t="s">
+        <v>89</v>
+      </c>
+      <c r="G26" t="s">
+        <v>14</v>
+      </c>
+      <c r="H26" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>82</v>
+      </c>
+      <c r="B27">
+        <v>2004</v>
+      </c>
+      <c r="C27" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" t="s">
+        <v>10</v>
+      </c>
+      <c r="E27" t="s">
+        <v>9</v>
+      </c>
+      <c r="F27" t="s">
+        <v>90</v>
+      </c>
+      <c r="G27" t="s">
+        <v>91</v>
+      </c>
+      <c r="H27" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>82</v>
+      </c>
+      <c r="B28">
+        <v>2006</v>
+      </c>
+      <c r="C28" t="s">
+        <v>17</v>
+      </c>
+      <c r="D28" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" t="s">
+        <v>10</v>
+      </c>
+      <c r="F28" t="s">
+        <v>93</v>
+      </c>
+      <c r="G28" t="s">
+        <v>68</v>
+      </c>
+      <c r="H28" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>82</v>
+      </c>
+      <c r="B29">
+        <v>2009</v>
+      </c>
+      <c r="C29" t="s">
+        <v>36</v>
+      </c>
+      <c r="D29" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" t="s">
+        <v>46</v>
+      </c>
+      <c r="F29" t="s">
+        <v>95</v>
+      </c>
+      <c r="G29" t="s">
+        <v>68</v>
+      </c>
+      <c r="H29" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>82</v>
+      </c>
+      <c r="B30">
+        <v>2013</v>
+      </c>
+      <c r="C30" t="s">
+        <v>50</v>
+      </c>
+      <c r="D30" t="s">
+        <v>17</v>
+      </c>
+      <c r="E30" t="s">
+        <v>9</v>
+      </c>
+      <c r="F30" t="s">
+        <v>96</v>
+      </c>
+      <c r="G30" t="s">
+        <v>97</v>
+      </c>
+      <c r="H30" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>82</v>
+      </c>
+      <c r="B31">
+        <v>2017</v>
+      </c>
+      <c r="C31" t="s">
+        <v>50</v>
+      </c>
+      <c r="D31" t="s">
+        <v>24</v>
+      </c>
+      <c r="E31" t="s">
+        <v>17</v>
+      </c>
+      <c r="F31" t="s">
+        <v>99</v>
+      </c>
+      <c r="G31" t="s">
+        <v>100</v>
+      </c>
+      <c r="H31" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>82</v>
+      </c>
+      <c r="B32">
+        <v>2025</v>
+      </c>
+      <c r="C32" t="s">
+        <v>102</v>
+      </c>
+      <c r="D32" t="s">
+        <v>17</v>
+      </c>
+      <c r="E32" t="s">
+        <v>46</v>
+      </c>
+      <c r="F32" t="s">
+        <v>103</v>
+      </c>
+      <c r="G32" t="s">
+        <v>104</v>
+      </c>
+      <c r="H32" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>82</v>
+      </c>
+      <c r="B33">
+        <v>2026</v>
+      </c>
+      <c r="C33" t="s">
+        <v>109</v>
+      </c>
+      <c r="D33" t="s">
+        <v>17</v>
+      </c>
+      <c r="E33" t="s">
+        <v>46</v>
+      </c>
+      <c r="F33" t="s">
+        <v>108</v>
+      </c>
+      <c r="G33" t="s">
+        <v>107</v>
+      </c>
+      <c r="H33" t="s">
+        <v>106</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/icc_dataset.xlsx
+++ b/icc_dataset.xlsx
@@ -8,20 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Downloads\Hrutik_pro1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52385C6A-C7F3-46C2-8996-F0C3EDE4BB0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4ADEF7B-8704-4022-8402-BDC1DA7CD50F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2460" windowWidth="20490" windowHeight="8460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="110">
   <si>
     <t>Tournament</t>
   </si>
@@ -1305,28 +1304,28 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="B24">
-        <v>1998</v>
+        <v>2026</v>
       </c>
       <c r="C24" t="s">
-        <v>69</v>
+        <v>109</v>
       </c>
       <c r="D24" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="E24" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="F24" t="s">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="G24" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="H24" t="s">
-        <v>84</v>
+        <v>106</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -1334,25 +1333,25 @@
         <v>82</v>
       </c>
       <c r="B25">
-        <v>2000</v>
+        <v>1998</v>
       </c>
       <c r="C25" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="D25" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="E25" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F25" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="G25" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="H25" t="s">
-        <v>14</v>
+        <v>84</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -1360,22 +1359,22 @@
         <v>82</v>
       </c>
       <c r="B26">
-        <v>2002</v>
+        <v>2000</v>
       </c>
       <c r="C26" t="s">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="D26" t="s">
-        <v>88</v>
+        <v>46</v>
       </c>
       <c r="E26" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F26" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G26" t="s">
-        <v>14</v>
+        <v>87</v>
       </c>
       <c r="H26" t="s">
         <v>14</v>
@@ -1386,25 +1385,25 @@
         <v>82</v>
       </c>
       <c r="B27">
-        <v>2004</v>
+        <v>2002</v>
       </c>
       <c r="C27" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="D27" t="s">
-        <v>10</v>
+        <v>88</v>
       </c>
       <c r="E27" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F27" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G27" t="s">
-        <v>91</v>
+        <v>14</v>
       </c>
       <c r="H27" t="s">
-        <v>92</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -1412,25 +1411,25 @@
         <v>82</v>
       </c>
       <c r="B28">
-        <v>2006</v>
+        <v>2004</v>
       </c>
       <c r="C28" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D28" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E28" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F28" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="G28" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="H28" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -1438,25 +1437,25 @@
         <v>82</v>
       </c>
       <c r="B29">
-        <v>2009</v>
+        <v>2006</v>
       </c>
       <c r="C29" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="D29" t="s">
         <v>11</v>
       </c>
       <c r="E29" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="F29" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G29" t="s">
         <v>68</v>
       </c>
       <c r="H29" t="s">
-        <v>38</v>
+        <v>94</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -1464,25 +1463,25 @@
         <v>82</v>
       </c>
       <c r="B30">
-        <v>2013</v>
+        <v>2009</v>
       </c>
       <c r="C30" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="D30" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E30" t="s">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="F30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G30" t="s">
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="H30" t="s">
-        <v>98</v>
+        <v>38</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -1490,25 +1489,25 @@
         <v>82</v>
       </c>
       <c r="B31">
-        <v>2017</v>
+        <v>2013</v>
       </c>
       <c r="C31" t="s">
         <v>50</v>
       </c>
       <c r="D31" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E31" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F31" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="G31" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H31" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -1516,25 +1515,25 @@
         <v>82</v>
       </c>
       <c r="B32">
-        <v>2025</v>
+        <v>2017</v>
       </c>
       <c r="C32" t="s">
-        <v>102</v>
+        <v>50</v>
       </c>
       <c r="D32" t="s">
+        <v>24</v>
+      </c>
+      <c r="E32" t="s">
         <v>17</v>
       </c>
-      <c r="E32" t="s">
-        <v>46</v>
-      </c>
       <c r="F32" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G32" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="H32" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -1542,10 +1541,10 @@
         <v>82</v>
       </c>
       <c r="B33">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C33" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="D33" t="s">
         <v>17</v>
@@ -1554,891 +1553,13 @@
         <v>46</v>
       </c>
       <c r="F33" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="G33" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="H33" t="s">
-        <v>106</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C70B37F-E10F-4D81-9B58-548484F1E08E}">
-  <dimension ref="A1:H33"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.28515625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2">
-        <v>1975</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3">
-        <v>1979</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4">
-        <v>1983</v>
-      </c>
-      <c r="C4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>1987</v>
-      </c>
-      <c r="C5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6">
-        <v>1992</v>
-      </c>
-      <c r="C6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7">
-        <v>1996</v>
-      </c>
-      <c r="C7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" t="s">
-        <v>30</v>
-      </c>
-      <c r="G7" t="s">
-        <v>31</v>
-      </c>
-      <c r="H7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
-        <v>1999</v>
-      </c>
-      <c r="C8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" t="s">
-        <v>33</v>
-      </c>
-      <c r="G8" t="s">
-        <v>34</v>
-      </c>
-      <c r="H8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9">
-        <v>2003</v>
-      </c>
-      <c r="C9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" t="s">
-        <v>17</v>
-      </c>
-      <c r="F9" t="s">
-        <v>37</v>
-      </c>
-      <c r="G9" t="s">
-        <v>38</v>
-      </c>
-      <c r="H9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10">
-        <v>2007</v>
-      </c>
-      <c r="C10" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" t="s">
-        <v>29</v>
-      </c>
-      <c r="F10" t="s">
-        <v>40</v>
-      </c>
-      <c r="G10" t="s">
-        <v>41</v>
-      </c>
-      <c r="H10" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11">
-        <v>2011</v>
-      </c>
-      <c r="C11" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" t="s">
-        <v>17</v>
-      </c>
-      <c r="E11" t="s">
-        <v>29</v>
-      </c>
-      <c r="F11" t="s">
-        <v>43</v>
-      </c>
-      <c r="G11" t="s">
-        <v>44</v>
-      </c>
-      <c r="H11" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12">
-        <v>2015</v>
-      </c>
-      <c r="C12" t="s">
-        <v>23</v>
-      </c>
-      <c r="D12" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" t="s">
-        <v>46</v>
-      </c>
-      <c r="F12" t="s">
-        <v>47</v>
-      </c>
-      <c r="G12" t="s">
-        <v>48</v>
-      </c>
-      <c r="H12" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13">
-        <v>2019</v>
-      </c>
-      <c r="C13" t="s">
-        <v>50</v>
-      </c>
-      <c r="D13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" t="s">
-        <v>46</v>
-      </c>
-      <c r="F13" t="s">
-        <v>51</v>
-      </c>
-      <c r="G13" t="s">
-        <v>52</v>
-      </c>
-      <c r="H13" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14">
-        <v>2023</v>
-      </c>
-      <c r="C14" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14" t="s">
-        <v>11</v>
-      </c>
-      <c r="E14" t="s">
-        <v>17</v>
-      </c>
-      <c r="F14" t="s">
-        <v>54</v>
-      </c>
-      <c r="G14" t="s">
-        <v>55</v>
-      </c>
-      <c r="H14" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>57</v>
-      </c>
-      <c r="B15">
-        <v>2007</v>
-      </c>
-      <c r="C15" t="s">
-        <v>36</v>
-      </c>
-      <c r="D15" t="s">
-        <v>17</v>
-      </c>
-      <c r="E15" t="s">
-        <v>24</v>
-      </c>
-      <c r="F15" t="s">
-        <v>58</v>
-      </c>
-      <c r="G15" t="s">
-        <v>59</v>
-      </c>
-      <c r="H15" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>57</v>
-      </c>
-      <c r="B16">
-        <v>2009</v>
-      </c>
-      <c r="C16" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" t="s">
-        <v>24</v>
-      </c>
-      <c r="E16" t="s">
-        <v>29</v>
-      </c>
-      <c r="F16" t="s">
-        <v>61</v>
-      </c>
-      <c r="G16" t="s">
-        <v>60</v>
-      </c>
-      <c r="H16" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>57</v>
-      </c>
-      <c r="B17">
-        <v>2010</v>
-      </c>
-      <c r="C17" t="s">
-        <v>10</v>
-      </c>
-      <c r="D17" t="s">
-        <v>9</v>
-      </c>
-      <c r="E17" t="s">
-        <v>11</v>
-      </c>
-      <c r="F17" t="s">
-        <v>63</v>
-      </c>
-      <c r="G17" t="s">
-        <v>64</v>
-      </c>
-      <c r="H17" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>57</v>
-      </c>
-      <c r="B18">
-        <v>2012</v>
-      </c>
-      <c r="C18" t="s">
-        <v>29</v>
-      </c>
-      <c r="D18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E18" t="s">
-        <v>29</v>
-      </c>
-      <c r="F18" t="s">
-        <v>66</v>
-      </c>
-      <c r="G18" t="s">
-        <v>67</v>
-      </c>
-      <c r="H18" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>57</v>
-      </c>
-      <c r="B19">
-        <v>2014</v>
-      </c>
-      <c r="C19" t="s">
-        <v>69</v>
-      </c>
-      <c r="D19" t="s">
-        <v>29</v>
-      </c>
-      <c r="E19" t="s">
-        <v>17</v>
-      </c>
-      <c r="F19" t="s">
-        <v>70</v>
-      </c>
-      <c r="G19" t="s">
-        <v>71</v>
-      </c>
-      <c r="H19" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>57</v>
-      </c>
-      <c r="B20">
-        <v>2016</v>
-      </c>
-      <c r="C20" t="s">
-        <v>17</v>
-      </c>
-      <c r="D20" t="s">
-        <v>10</v>
-      </c>
-      <c r="E20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" t="s">
-        <v>72</v>
-      </c>
-      <c r="G20" t="s">
-        <v>67</v>
-      </c>
-      <c r="H20" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>57</v>
-      </c>
-      <c r="B21">
-        <v>2021</v>
-      </c>
-      <c r="C21" t="s">
-        <v>73</v>
-      </c>
-      <c r="D21" t="s">
-        <v>11</v>
-      </c>
-      <c r="E21" t="s">
-        <v>46</v>
-      </c>
-      <c r="F21" t="s">
-        <v>74</v>
-      </c>
-      <c r="G21" t="s">
-        <v>75</v>
-      </c>
-      <c r="H21" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>57</v>
-      </c>
-      <c r="B22">
-        <v>2022</v>
-      </c>
-      <c r="C22" t="s">
-        <v>11</v>
-      </c>
-      <c r="D22" t="s">
-        <v>9</v>
-      </c>
-      <c r="E22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F22" t="s">
-        <v>77</v>
-      </c>
-      <c r="G22" t="s">
-        <v>78</v>
-      </c>
-      <c r="H22" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>57</v>
-      </c>
-      <c r="B23">
-        <v>2024</v>
-      </c>
-      <c r="C23" t="s">
-        <v>79</v>
-      </c>
-      <c r="D23" t="s">
-        <v>17</v>
-      </c>
-      <c r="E23" t="s">
-        <v>36</v>
-      </c>
-      <c r="F23" t="s">
-        <v>80</v>
-      </c>
-      <c r="G23" t="s">
-        <v>56</v>
-      </c>
-      <c r="H23" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>82</v>
-      </c>
-      <c r="B24">
-        <v>1998</v>
-      </c>
-      <c r="C24" t="s">
-        <v>69</v>
-      </c>
-      <c r="D24" t="s">
-        <v>36</v>
-      </c>
-      <c r="E24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" t="s">
-        <v>83</v>
-      </c>
-      <c r="G24" t="s">
-        <v>84</v>
-      </c>
-      <c r="H24" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>82</v>
-      </c>
-      <c r="B25">
-        <v>2000</v>
-      </c>
-      <c r="C25" t="s">
-        <v>85</v>
-      </c>
-      <c r="D25" t="s">
-        <v>46</v>
-      </c>
-      <c r="E25" t="s">
-        <v>17</v>
-      </c>
-      <c r="F25" t="s">
-        <v>86</v>
-      </c>
-      <c r="G25" t="s">
-        <v>87</v>
-      </c>
-      <c r="H25" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>82</v>
-      </c>
-      <c r="B26">
-        <v>2002</v>
-      </c>
-      <c r="C26" t="s">
-        <v>29</v>
-      </c>
-      <c r="D26" t="s">
-        <v>88</v>
-      </c>
-      <c r="E26" t="s">
-        <v>14</v>
-      </c>
-      <c r="F26" t="s">
-        <v>89</v>
-      </c>
-      <c r="G26" t="s">
-        <v>14</v>
-      </c>
-      <c r="H26" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>82</v>
-      </c>
-      <c r="B27">
-        <v>2004</v>
-      </c>
-      <c r="C27" t="s">
-        <v>9</v>
-      </c>
-      <c r="D27" t="s">
-        <v>10</v>
-      </c>
-      <c r="E27" t="s">
-        <v>9</v>
-      </c>
-      <c r="F27" t="s">
-        <v>90</v>
-      </c>
-      <c r="G27" t="s">
-        <v>91</v>
-      </c>
-      <c r="H27" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>82</v>
-      </c>
-      <c r="B28">
-        <v>2006</v>
-      </c>
-      <c r="C28" t="s">
-        <v>17</v>
-      </c>
-      <c r="D28" t="s">
-        <v>11</v>
-      </c>
-      <c r="E28" t="s">
-        <v>10</v>
-      </c>
-      <c r="F28" t="s">
-        <v>93</v>
-      </c>
-      <c r="G28" t="s">
-        <v>68</v>
-      </c>
-      <c r="H28" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>82</v>
-      </c>
-      <c r="B29">
-        <v>2009</v>
-      </c>
-      <c r="C29" t="s">
-        <v>36</v>
-      </c>
-      <c r="D29" t="s">
-        <v>11</v>
-      </c>
-      <c r="E29" t="s">
-        <v>46</v>
-      </c>
-      <c r="F29" t="s">
-        <v>95</v>
-      </c>
-      <c r="G29" t="s">
-        <v>68</v>
-      </c>
-      <c r="H29" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>82</v>
-      </c>
-      <c r="B30">
-        <v>2013</v>
-      </c>
-      <c r="C30" t="s">
-        <v>50</v>
-      </c>
-      <c r="D30" t="s">
-        <v>17</v>
-      </c>
-      <c r="E30" t="s">
-        <v>9</v>
-      </c>
-      <c r="F30" t="s">
-        <v>96</v>
-      </c>
-      <c r="G30" t="s">
-        <v>97</v>
-      </c>
-      <c r="H30" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>82</v>
-      </c>
-      <c r="B31">
-        <v>2017</v>
-      </c>
-      <c r="C31" t="s">
-        <v>50</v>
-      </c>
-      <c r="D31" t="s">
-        <v>24</v>
-      </c>
-      <c r="E31" t="s">
-        <v>17</v>
-      </c>
-      <c r="F31" t="s">
-        <v>99</v>
-      </c>
-      <c r="G31" t="s">
-        <v>100</v>
-      </c>
-      <c r="H31" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>82</v>
-      </c>
-      <c r="B32">
-        <v>2025</v>
-      </c>
-      <c r="C32" t="s">
-        <v>102</v>
-      </c>
-      <c r="D32" t="s">
-        <v>17</v>
-      </c>
-      <c r="E32" t="s">
-        <v>46</v>
-      </c>
-      <c r="F32" t="s">
-        <v>103</v>
-      </c>
-      <c r="G32" t="s">
-        <v>104</v>
-      </c>
-      <c r="H32" t="s">
         <v>105</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>82</v>
-      </c>
-      <c r="B33">
-        <v>2026</v>
-      </c>
-      <c r="C33" t="s">
-        <v>109</v>
-      </c>
-      <c r="D33" t="s">
-        <v>17</v>
-      </c>
-      <c r="E33" t="s">
-        <v>46</v>
-      </c>
-      <c r="F33" t="s">
-        <v>108</v>
-      </c>
-      <c r="G33" t="s">
-        <v>107</v>
-      </c>
-      <c r="H33" t="s">
-        <v>106</v>
       </c>
     </row>
   </sheetData>
